--- a/tuning/compare_pv_ft_seg.xlsx
+++ b/tuning/compare_pv_ft_seg.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="324" windowWidth="21768" windowHeight="10596" tabRatio="850" firstSheet="2" activeTab="11"/>
+    <workbookView xWindow="768" yWindow="324" windowWidth="21768" windowHeight="10596" tabRatio="850" firstSheet="2" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="synth_new2_test" sheetId="1" r:id="rId1"/>
@@ -55,8 +55,8 @@
   </definedNames>
   <calcPr calcId="125725"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId17"/>
-    <pivotCache cacheId="7" r:id="rId18"/>
+    <pivotCache cacheId="8" r:id="rId17"/>
+    <pivotCache cacheId="9" r:id="rId18"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -704,12 +704,24 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -749,7 +761,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -763,6 +775,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Dziesiętny" xfId="1" builtinId="3"/>
@@ -3198,7 +3215,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H1:I26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -3355,7 +3372,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E1:F72" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -11014,10 +11031,10 @@
         <f t="shared" ref="P2:P65" si="0">C2</f>
         <v>finloop</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="15" t="s">
         <v>78</v>
       </c>
       <c r="S2" s="8" t="str">
@@ -11079,10 +11096,10 @@
         <f t="shared" si="0"/>
         <v>ft21SGD</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="15" t="s">
         <v>87</v>
       </c>
       <c r="S3" s="8" t="str">
@@ -11274,10 +11291,10 @@
         <f t="shared" si="0"/>
         <v>ft27_SGD_finloop.pt</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="15" t="s">
         <v>87</v>
       </c>
       <c r="S6" s="8" t="str">
@@ -11599,10 +11616,10 @@
         <f t="shared" si="0"/>
         <v>ft27_AdamW_finloop.pt</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="R11" s="15" t="s">
         <v>88</v>
       </c>
       <c r="S11" s="8" t="str">
@@ -15005,7 +15022,7 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="A2" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B2" t="s">
@@ -15054,10 +15071,10 @@
         <f t="shared" ref="P2:P65" si="0">C2</f>
         <v>finloop</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="15" t="s">
         <v>78</v>
       </c>
       <c r="S2" s="8" t="str">
@@ -15070,7 +15087,7 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" t="s">
+      <c r="A3" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B3" t="s">
@@ -15119,10 +15136,10 @@
         <f t="shared" si="0"/>
         <v>ft21SGD</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="15" t="s">
         <v>87</v>
       </c>
       <c r="S3" s="8" t="str">
@@ -15135,7 +15152,7 @@
       </c>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" t="s">
+      <c r="A4" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B4" t="s">
@@ -15200,7 +15217,7 @@
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" t="s">
+      <c r="A5" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B5" t="s">
@@ -15265,7 +15282,7 @@
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" t="s">
+      <c r="A6" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B6" t="s">
@@ -15314,10 +15331,10 @@
         <f t="shared" si="0"/>
         <v>ft29_SGD</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="15" t="s">
         <v>87</v>
       </c>
       <c r="S6" s="8" t="str">
@@ -15330,7 +15347,7 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" t="s">
+      <c r="A7" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B7" t="s">
@@ -15395,7 +15412,7 @@
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" t="s">
+      <c r="A8" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B8" t="s">
@@ -15460,7 +15477,7 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" t="s">
+      <c r="A9" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B9" t="s">
@@ -15525,7 +15542,7 @@
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" t="s">
+      <c r="A10" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B10" t="s">
@@ -15590,7 +15607,7 @@
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" t="s">
+      <c r="A11" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B11" t="s">
@@ -15639,10 +15656,10 @@
         <f t="shared" si="0"/>
         <v>ft30_SGD_finloop.pt</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="R11" s="15" t="s">
         <v>88</v>
       </c>
       <c r="S11" s="8" t="str">
@@ -15655,7 +15672,7 @@
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" t="s">
+      <c r="A12" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B12" t="s">
@@ -15706,7 +15723,7 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" t="s">
+      <c r="A13" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B13" t="s">
@@ -15757,7 +15774,7 @@
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" t="s">
+      <c r="A14" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B14" t="s">
@@ -15808,7 +15825,7 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" t="s">
+      <c r="A15" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B15" t="s">
@@ -15859,7 +15876,7 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" t="s">
+      <c r="A16" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B16" t="s">
@@ -15910,7 +15927,7 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" t="s">
+      <c r="A17" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B17" t="s">
@@ -15961,7 +15978,7 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" t="s">
+      <c r="A18" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B18" t="s">
@@ -16012,7 +16029,7 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" t="s">
+      <c r="A19" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B19" t="s">
@@ -16063,7 +16080,7 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" t="s">
+      <c r="A20" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B20" t="s">
@@ -16114,7 +16131,7 @@
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" t="s">
+      <c r="A21" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B21" t="s">
@@ -16165,7 +16182,7 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" t="s">
+      <c r="A22" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B22" t="s">
@@ -16216,7 +16233,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" s="7" customFormat="1">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="12" t="s">
         <v>77</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -16267,7 +16284,7 @@
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" t="s">
+      <c r="A24" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B24" t="s">
@@ -16318,7 +16335,7 @@
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" t="s">
+      <c r="A25" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B25" t="s">
@@ -16369,7 +16386,7 @@
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" t="s">
+      <c r="A26" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B26" t="s">
@@ -16420,7 +16437,7 @@
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" t="s">
+      <c r="A27" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B27" t="s">
@@ -16471,7 +16488,7 @@
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" t="s">
+      <c r="A28" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B28" t="s">
@@ -16522,7 +16539,7 @@
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" t="s">
+      <c r="A29" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B29" t="s">
@@ -16573,7 +16590,7 @@
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" t="s">
+      <c r="A30" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B30" t="s">
@@ -16624,7 +16641,7 @@
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" t="s">
+      <c r="A31" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B31" t="s">
@@ -16675,7 +16692,7 @@
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" t="s">
+      <c r="A32" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B32" t="s">
@@ -16726,7 +16743,7 @@
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" t="s">
+      <c r="A33" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B33" t="s">
@@ -16777,7 +16794,7 @@
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" t="s">
+      <c r="A34" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B34" t="s">
@@ -16828,7 +16845,7 @@
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" t="s">
+      <c r="A35" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B35" t="s">
@@ -16879,7 +16896,7 @@
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" t="s">
+      <c r="A36" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B36" t="s">
@@ -16930,7 +16947,7 @@
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" t="s">
+      <c r="A37" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B37" t="s">
@@ -16981,7 +16998,7 @@
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" t="s">
+      <c r="A38" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B38" t="s">
@@ -17032,7 +17049,7 @@
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" t="s">
+      <c r="A39" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B39" t="s">
@@ -17083,7 +17100,7 @@
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" t="s">
+      <c r="A40" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B40" t="s">
@@ -17134,7 +17151,7 @@
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" t="s">
+      <c r="A41" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B41" t="s">
@@ -17185,7 +17202,7 @@
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" t="s">
+      <c r="A42" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B42" t="s">
@@ -17236,7 +17253,7 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" t="s">
+      <c r="A43" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B43" t="s">
@@ -17287,7 +17304,7 @@
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" t="s">
+      <c r="A44" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B44" t="s">
@@ -17338,7 +17355,7 @@
       </c>
     </row>
     <row r="45" spans="1:16" s="7" customFormat="1">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="14" t="s">
         <v>86</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -19633,7 +19650,7 @@
       </c>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" t="s">
+      <c r="A90" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B90" t="s">
@@ -19684,7 +19701,7 @@
       </c>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" t="s">
+      <c r="A91" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B91" t="s">
@@ -19735,7 +19752,7 @@
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" t="s">
+      <c r="A92" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B92" t="s">
@@ -19786,7 +19803,7 @@
       </c>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" t="s">
+      <c r="A93" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B93" t="s">
@@ -19837,7 +19854,7 @@
       </c>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" t="s">
+      <c r="A94" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B94" t="s">
@@ -19888,7 +19905,7 @@
       </c>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" t="s">
+      <c r="A95" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B95" t="s">
@@ -19939,7 +19956,7 @@
       </c>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" t="s">
+      <c r="A96" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B96" t="s">
@@ -19990,7 +20007,7 @@
       </c>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" t="s">
+      <c r="A97" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B97" t="s">
@@ -20041,7 +20058,7 @@
       </c>
     </row>
     <row r="98" spans="1:16">
-      <c r="A98" t="s">
+      <c r="A98" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B98" t="s">
@@ -20092,7 +20109,7 @@
       </c>
     </row>
     <row r="99" spans="1:16">
-      <c r="A99" t="s">
+      <c r="A99" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B99" t="s">
@@ -20143,7 +20160,7 @@
       </c>
     </row>
     <row r="100" spans="1:16">
-      <c r="A100" t="s">
+      <c r="A100" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B100" t="s">
@@ -20194,7 +20211,7 @@
       </c>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" t="s">
+      <c r="A101" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B101" t="s">
@@ -20245,7 +20262,7 @@
       </c>
     </row>
     <row r="102" spans="1:16">
-      <c r="A102" t="s">
+      <c r="A102" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B102" t="s">
@@ -20296,7 +20313,7 @@
       </c>
     </row>
     <row r="103" spans="1:16">
-      <c r="A103" t="s">
+      <c r="A103" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B103" t="s">
@@ -20347,7 +20364,7 @@
       </c>
     </row>
     <row r="104" spans="1:16">
-      <c r="A104" t="s">
+      <c r="A104" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B104" t="s">
@@ -20398,7 +20415,7 @@
       </c>
     </row>
     <row r="105" spans="1:16">
-      <c r="A105" t="s">
+      <c r="A105" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B105" t="s">
@@ -20449,7 +20466,7 @@
       </c>
     </row>
     <row r="106" spans="1:16">
-      <c r="A106" t="s">
+      <c r="A106" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B106" t="s">
@@ -20500,7 +20517,7 @@
       </c>
     </row>
     <row r="107" spans="1:16">
-      <c r="A107" t="s">
+      <c r="A107" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B107" t="s">
@@ -20551,7 +20568,7 @@
       </c>
     </row>
     <row r="108" spans="1:16">
-      <c r="A108" t="s">
+      <c r="A108" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B108" t="s">
@@ -20602,7 +20619,7 @@
       </c>
     </row>
     <row r="109" spans="1:16">
-      <c r="A109" t="s">
+      <c r="A109" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B109" t="s">
@@ -20653,7 +20670,7 @@
       </c>
     </row>
     <row r="110" spans="1:16">
-      <c r="A110" t="s">
+      <c r="A110" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B110" t="s">
@@ -20704,7 +20721,7 @@
       </c>
     </row>
     <row r="111" spans="1:16" s="7" customFormat="1">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="14" t="s">
         <v>89</v>
       </c>
       <c r="B111" s="7" t="s">
@@ -25243,7 +25260,7 @@
       </c>
     </row>
     <row r="200" spans="1:16">
-      <c r="A200" t="s">
+      <c r="A200" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B200" t="s">
@@ -25294,7 +25311,7 @@
       </c>
     </row>
     <row r="201" spans="1:16">
-      <c r="A201" t="s">
+      <c r="A201" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B201" t="s">
@@ -25345,7 +25362,7 @@
       </c>
     </row>
     <row r="202" spans="1:16">
-      <c r="A202" t="s">
+      <c r="A202" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B202" t="s">
@@ -25396,7 +25413,7 @@
       </c>
     </row>
     <row r="203" spans="1:16">
-      <c r="A203" t="s">
+      <c r="A203" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B203" t="s">
@@ -25447,7 +25464,7 @@
       </c>
     </row>
     <row r="204" spans="1:16">
-      <c r="A204" t="s">
+      <c r="A204" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B204" t="s">
@@ -25498,7 +25515,7 @@
       </c>
     </row>
     <row r="205" spans="1:16">
-      <c r="A205" t="s">
+      <c r="A205" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B205" t="s">
@@ -25549,7 +25566,7 @@
       </c>
     </row>
     <row r="206" spans="1:16">
-      <c r="A206" t="s">
+      <c r="A206" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B206" t="s">
@@ -25600,7 +25617,7 @@
       </c>
     </row>
     <row r="207" spans="1:16">
-      <c r="A207" t="s">
+      <c r="A207" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B207" t="s">
@@ -25651,7 +25668,7 @@
       </c>
     </row>
     <row r="208" spans="1:16">
-      <c r="A208" t="s">
+      <c r="A208" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B208" t="s">
@@ -25702,7 +25719,7 @@
       </c>
     </row>
     <row r="209" spans="1:16">
-      <c r="A209" t="s">
+      <c r="A209" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B209" t="s">
@@ -25753,7 +25770,7 @@
       </c>
     </row>
     <row r="210" spans="1:16">
-      <c r="A210" t="s">
+      <c r="A210" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B210" t="s">
@@ -25804,7 +25821,7 @@
       </c>
     </row>
     <row r="211" spans="1:16">
-      <c r="A211" t="s">
+      <c r="A211" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B211" t="s">
@@ -25855,7 +25872,7 @@
       </c>
     </row>
     <row r="212" spans="1:16">
-      <c r="A212" t="s">
+      <c r="A212" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B212" t="s">
@@ -25906,7 +25923,7 @@
       </c>
     </row>
     <row r="213" spans="1:16">
-      <c r="A213" t="s">
+      <c r="A213" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B213" t="s">
@@ -25957,7 +25974,7 @@
       </c>
     </row>
     <row r="214" spans="1:16">
-      <c r="A214" t="s">
+      <c r="A214" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B214" t="s">
@@ -26008,7 +26025,7 @@
       </c>
     </row>
     <row r="215" spans="1:16">
-      <c r="A215" t="s">
+      <c r="A215" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B215" t="s">
@@ -26059,7 +26076,7 @@
       </c>
     </row>
     <row r="216" spans="1:16">
-      <c r="A216" t="s">
+      <c r="A216" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B216" t="s">
@@ -26110,7 +26127,7 @@
       </c>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" t="s">
+      <c r="A217" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B217" t="s">
@@ -26161,7 +26178,7 @@
       </c>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" t="s">
+      <c r="A218" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B218" t="s">
@@ -26212,7 +26229,7 @@
       </c>
     </row>
     <row r="219" spans="1:16">
-      <c r="A219" t="s">
+      <c r="A219" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B219" t="s">
@@ -26263,7 +26280,7 @@
       </c>
     </row>
     <row r="220" spans="1:16">
-      <c r="A220" t="s">
+      <c r="A220" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B220" t="s">
@@ -26314,7 +26331,7 @@
       </c>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" t="s">
+      <c r="A221" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B221" t="s">
